--- a/2. Documentation/0. Project Details/Timeline.xlsx
+++ b/2. Documentation/0. Project Details/Timeline.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fc6206cd76c8efb5/Documents/SCHOOL_TECH/1-Current Courses/Capstone I/1. Git Repo/S26_Team6_LaniEV-RetroFit/2. Documentation/0. Project Details/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="8_{09987254-AD0E-4C28-A73A-9075852F49BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8088376-45FA-4130-B63B-CC5A2139E6C0}"/>
+  <xr:revisionPtr revIDLastSave="50" documentId="8_{09987254-AD0E-4C28-A73A-9075852F49BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1402EFFE-03D3-46A1-9365-CC7FB34A3BAE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -720,7 +720,7 @@
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -861,6 +861,53 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="8" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="6" xfId="11" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="9" borderId="6" xfId="9" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="6" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -870,10 +917,13 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -885,6 +935,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="166" fontId="14" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -894,68 +947,12 @@
     <xf numFmtId="166" fontId="14" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="166" fontId="14" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="14" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="16" fillId="8" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="14" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="6" xfId="11" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="9" borderId="6" xfId="9" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="6" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="Comma" xfId="3" builtinId="3" customBuiltin="1"/>
@@ -971,7 +968,7 @@
     <cellStyle name="Title" xfId="4" builtinId="15" customBuiltin="1"/>
     <cellStyle name="zHiddenText" xfId="2" xr:uid="{26E66EE6-E33F-4D77-BAE4-0FB4F5BBF673}"/>
   </cellStyles>
-  <dxfs count="42">
+  <dxfs count="20">
     <dxf>
       <fill>
         <patternFill>
@@ -1002,6 +999,18 @@
         <bottom style="thin">
           <color theme="0" tint="-4.9989318521683403E-2"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="5"/>
+        </left>
+        <right style="thin">
+          <color theme="5"/>
+        </right>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1117,326 +1126,6 @@
     <dxf>
       <border>
         <left style="thin">
-          <color theme="5"/>
-        </left>
-        <right style="thin">
-          <color theme="5"/>
-        </right>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.499984740745262"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color theme="5"/>
-        </left>
-        <right style="thin">
-          <color theme="5"/>
-        </right>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color theme="5"/>
-        </left>
-        <right style="thin">
-          <color theme="5"/>
-        </right>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
           <color theme="0" tint="-0.24994659260841701"/>
         </left>
       </border>
@@ -1530,15 +1219,15 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="ToDoList" pivot="0" count="9" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" dxfId="41"/>
-      <tableStyleElement type="headerRow" dxfId="40"/>
-      <tableStyleElement type="totalRow" dxfId="39"/>
-      <tableStyleElement type="firstColumn" dxfId="38"/>
-      <tableStyleElement type="lastColumn" dxfId="37"/>
-      <tableStyleElement type="firstRowStripe" dxfId="36"/>
-      <tableStyleElement type="secondRowStripe" dxfId="35"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="34"/>
-      <tableStyleElement type="secondColumnStripe" dxfId="33"/>
+      <tableStyleElement type="wholeTable" dxfId="19"/>
+      <tableStyleElement type="headerRow" dxfId="18"/>
+      <tableStyleElement type="totalRow" dxfId="17"/>
+      <tableStyleElement type="firstColumn" dxfId="16"/>
+      <tableStyleElement type="lastColumn" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="secondRowStripe" dxfId="13"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="12"/>
+      <tableStyleElement type="secondColumnStripe" dxfId="11"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -1893,7 +1582,7 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:ER16"/>
+  <dimension ref="A1:DO16"/>
   <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.69921875" style="12" customWidth="1"/>
@@ -1906,256 +1595,256 @@
     <col min="8" max="173" width="2.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:148" ht="90" customHeight="1" x14ac:dyDescent="1.45">
+    <row r="1" spans="1:119" ht="90" customHeight="1" x14ac:dyDescent="1.45">
       <c r="A1" s="13"/>
-      <c r="B1" s="65" t="s">
+      <c r="B1" s="80" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="60" t="s">
+      <c r="H1" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="61"/>
-      <c r="J1" s="61"/>
-      <c r="K1" s="61"/>
-      <c r="L1" s="61"/>
-      <c r="M1" s="61"/>
-      <c r="N1" s="61"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
+      <c r="M1" s="79"/>
+      <c r="N1" s="79"/>
       <c r="O1" s="18"/>
-      <c r="P1" s="59">
+      <c r="P1" s="77">
         <v>46050</v>
       </c>
-      <c r="Q1" s="58"/>
-      <c r="R1" s="58"/>
-      <c r="S1" s="58"/>
-      <c r="T1" s="58"/>
-      <c r="U1" s="58"/>
-      <c r="V1" s="58"/>
-      <c r="W1" s="58"/>
-      <c r="X1" s="58"/>
-      <c r="Y1" s="58"/>
+      <c r="Q1" s="76"/>
+      <c r="R1" s="76"/>
+      <c r="S1" s="76"/>
+      <c r="T1" s="76"/>
+      <c r="U1" s="76"/>
+      <c r="V1" s="76"/>
+      <c r="W1" s="76"/>
+      <c r="X1" s="76"/>
+      <c r="Y1" s="76"/>
     </row>
-    <row r="2" spans="1:148" ht="30" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B2" s="66" t="s">
+    <row r="2" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="B2" s="52" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="66"/>
+      <c r="C2" s="52"/>
       <c r="D2" s="17"/>
       <c r="E2" s="16"/>
-      <c r="H2" s="60" t="s">
+      <c r="H2" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61"/>
-      <c r="M2" s="61"/>
-      <c r="N2" s="61"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
+      <c r="L2" s="79"/>
+      <c r="M2" s="79"/>
+      <c r="N2" s="79"/>
       <c r="O2" s="18"/>
-      <c r="P2" s="57">
+      <c r="P2" s="75">
         <v>1</v>
       </c>
-      <c r="Q2" s="58"/>
-      <c r="R2" s="58"/>
-      <c r="S2" s="58"/>
-      <c r="T2" s="58"/>
-      <c r="U2" s="58"/>
-      <c r="V2" s="58"/>
-      <c r="W2" s="58"/>
-      <c r="X2" s="58"/>
-      <c r="Y2" s="58"/>
+      <c r="Q2" s="76"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="76"/>
+      <c r="U2" s="76"/>
+      <c r="V2" s="76"/>
+      <c r="W2" s="76"/>
+      <c r="X2" s="76"/>
+      <c r="Y2" s="76"/>
     </row>
-    <row r="3" spans="1:148" s="19" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:119" s="19" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
-      <c r="B3" s="74" t="s">
+      <c r="B3" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="74"/>
+      <c r="C3" s="57"/>
       <c r="D3" s="20"/>
     </row>
-    <row r="4" spans="1:148" s="19" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:119" s="19" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13"/>
-      <c r="B4" s="84"/>
-      <c r="C4" s="84"/>
-      <c r="D4" s="85"/>
-      <c r="E4" s="86"/>
-      <c r="F4" s="86"/>
-      <c r="H4" s="64">
+      <c r="B4" s="66"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="H4" s="83">
         <f>H5</f>
         <v>46048</v>
       </c>
-      <c r="I4" s="62"/>
-      <c r="J4" s="62"/>
-      <c r="K4" s="62"/>
-      <c r="L4" s="62"/>
-      <c r="M4" s="62"/>
-      <c r="N4" s="62"/>
-      <c r="O4" s="62">
+      <c r="I4" s="81"/>
+      <c r="J4" s="81"/>
+      <c r="K4" s="81"/>
+      <c r="L4" s="81"/>
+      <c r="M4" s="81"/>
+      <c r="N4" s="81"/>
+      <c r="O4" s="81">
         <f>O5</f>
         <v>46055</v>
       </c>
-      <c r="P4" s="62"/>
-      <c r="Q4" s="62"/>
-      <c r="R4" s="62"/>
-      <c r="S4" s="62"/>
-      <c r="T4" s="62"/>
-      <c r="U4" s="62"/>
-      <c r="V4" s="62">
+      <c r="P4" s="81"/>
+      <c r="Q4" s="81"/>
+      <c r="R4" s="81"/>
+      <c r="S4" s="81"/>
+      <c r="T4" s="81"/>
+      <c r="U4" s="81"/>
+      <c r="V4" s="81">
         <f>V5</f>
         <v>46062</v>
       </c>
-      <c r="W4" s="62"/>
-      <c r="X4" s="62"/>
-      <c r="Y4" s="62"/>
-      <c r="Z4" s="62"/>
-      <c r="AA4" s="62"/>
-      <c r="AB4" s="62"/>
-      <c r="AC4" s="62">
+      <c r="W4" s="81"/>
+      <c r="X4" s="81"/>
+      <c r="Y4" s="81"/>
+      <c r="Z4" s="81"/>
+      <c r="AA4" s="81"/>
+      <c r="AB4" s="81"/>
+      <c r="AC4" s="81">
         <f>AC5</f>
         <v>46069</v>
       </c>
-      <c r="AD4" s="62"/>
-      <c r="AE4" s="62"/>
-      <c r="AF4" s="62"/>
-      <c r="AG4" s="62"/>
-      <c r="AH4" s="62"/>
-      <c r="AI4" s="62"/>
-      <c r="AJ4" s="62">
+      <c r="AD4" s="81"/>
+      <c r="AE4" s="81"/>
+      <c r="AF4" s="81"/>
+      <c r="AG4" s="81"/>
+      <c r="AH4" s="81"/>
+      <c r="AI4" s="81"/>
+      <c r="AJ4" s="81">
         <f>AJ5</f>
         <v>46076</v>
       </c>
-      <c r="AK4" s="62"/>
-      <c r="AL4" s="62"/>
-      <c r="AM4" s="62"/>
-      <c r="AN4" s="62"/>
-      <c r="AO4" s="62"/>
-      <c r="AP4" s="62"/>
-      <c r="AQ4" s="62">
+      <c r="AK4" s="81"/>
+      <c r="AL4" s="81"/>
+      <c r="AM4" s="81"/>
+      <c r="AN4" s="81"/>
+      <c r="AO4" s="81"/>
+      <c r="AP4" s="81"/>
+      <c r="AQ4" s="81">
         <f>AQ5</f>
         <v>46083</v>
       </c>
-      <c r="AR4" s="62"/>
-      <c r="AS4" s="62"/>
-      <c r="AT4" s="62"/>
-      <c r="AU4" s="62"/>
-      <c r="AV4" s="62"/>
-      <c r="AW4" s="62"/>
-      <c r="AX4" s="62">
+      <c r="AR4" s="81"/>
+      <c r="AS4" s="81"/>
+      <c r="AT4" s="81"/>
+      <c r="AU4" s="81"/>
+      <c r="AV4" s="81"/>
+      <c r="AW4" s="81"/>
+      <c r="AX4" s="81">
         <f>AX5</f>
         <v>46090</v>
       </c>
-      <c r="AY4" s="62"/>
-      <c r="AZ4" s="62"/>
-      <c r="BA4" s="62"/>
-      <c r="BB4" s="62"/>
-      <c r="BC4" s="62"/>
-      <c r="BD4" s="62"/>
-      <c r="BE4" s="62">
+      <c r="AY4" s="81"/>
+      <c r="AZ4" s="81"/>
+      <c r="BA4" s="81"/>
+      <c r="BB4" s="81"/>
+      <c r="BC4" s="81"/>
+      <c r="BD4" s="81"/>
+      <c r="BE4" s="81">
         <f>BE5</f>
         <v>46097</v>
       </c>
-      <c r="BF4" s="62"/>
-      <c r="BG4" s="62"/>
-      <c r="BH4" s="62"/>
-      <c r="BI4" s="62"/>
-      <c r="BJ4" s="62"/>
-      <c r="BK4" s="63"/>
-      <c r="BL4" s="67">
+      <c r="BF4" s="81"/>
+      <c r="BG4" s="81"/>
+      <c r="BH4" s="81"/>
+      <c r="BI4" s="81"/>
+      <c r="BJ4" s="81"/>
+      <c r="BK4" s="82"/>
+      <c r="BL4" s="85">
         <f>BL5</f>
         <v>46104</v>
       </c>
-      <c r="BM4" s="62"/>
-      <c r="BN4" s="62"/>
-      <c r="BO4" s="62"/>
-      <c r="BP4" s="62"/>
-      <c r="BQ4" s="62"/>
-      <c r="BR4" s="62"/>
-      <c r="BS4" s="62">
+      <c r="BM4" s="81"/>
+      <c r="BN4" s="81"/>
+      <c r="BO4" s="81"/>
+      <c r="BP4" s="81"/>
+      <c r="BQ4" s="81"/>
+      <c r="BR4" s="81"/>
+      <c r="BS4" s="81">
         <f>BS5</f>
         <v>46111</v>
       </c>
-      <c r="BT4" s="62"/>
-      <c r="BU4" s="62"/>
-      <c r="BV4" s="62"/>
-      <c r="BW4" s="62"/>
-      <c r="BX4" s="62"/>
-      <c r="BY4" s="62"/>
-      <c r="BZ4" s="62">
+      <c r="BT4" s="81"/>
+      <c r="BU4" s="81"/>
+      <c r="BV4" s="81"/>
+      <c r="BW4" s="81"/>
+      <c r="BX4" s="81"/>
+      <c r="BY4" s="81"/>
+      <c r="BZ4" s="81">
         <f>BZ5</f>
         <v>46118</v>
       </c>
-      <c r="CA4" s="62"/>
-      <c r="CB4" s="62"/>
-      <c r="CC4" s="62"/>
-      <c r="CD4" s="62"/>
-      <c r="CE4" s="62"/>
-      <c r="CF4" s="62"/>
-      <c r="CG4" s="62">
+      <c r="CA4" s="81"/>
+      <c r="CB4" s="81"/>
+      <c r="CC4" s="81"/>
+      <c r="CD4" s="81"/>
+      <c r="CE4" s="81"/>
+      <c r="CF4" s="81"/>
+      <c r="CG4" s="81">
         <f>CG5</f>
         <v>46125</v>
       </c>
-      <c r="CH4" s="62"/>
-      <c r="CI4" s="62"/>
-      <c r="CJ4" s="62"/>
-      <c r="CK4" s="62"/>
-      <c r="CL4" s="62"/>
-      <c r="CM4" s="62"/>
-      <c r="CN4" s="62">
+      <c r="CH4" s="81"/>
+      <c r="CI4" s="81"/>
+      <c r="CJ4" s="81"/>
+      <c r="CK4" s="81"/>
+      <c r="CL4" s="81"/>
+      <c r="CM4" s="81"/>
+      <c r="CN4" s="81">
         <f>CN5</f>
         <v>46132</v>
       </c>
-      <c r="CO4" s="62"/>
-      <c r="CP4" s="62"/>
-      <c r="CQ4" s="62"/>
-      <c r="CR4" s="62"/>
-      <c r="CS4" s="62"/>
-      <c r="CT4" s="62"/>
-      <c r="CU4" s="62">
+      <c r="CO4" s="81"/>
+      <c r="CP4" s="81"/>
+      <c r="CQ4" s="81"/>
+      <c r="CR4" s="81"/>
+      <c r="CS4" s="81"/>
+      <c r="CT4" s="81"/>
+      <c r="CU4" s="81">
         <f>CU5</f>
         <v>46139</v>
       </c>
-      <c r="CV4" s="62"/>
-      <c r="CW4" s="62"/>
-      <c r="CX4" s="62"/>
-      <c r="CY4" s="62"/>
-      <c r="CZ4" s="62"/>
-      <c r="DA4" s="62"/>
-      <c r="DB4" s="62">
+      <c r="CV4" s="81"/>
+      <c r="CW4" s="81"/>
+      <c r="CX4" s="81"/>
+      <c r="CY4" s="81"/>
+      <c r="CZ4" s="81"/>
+      <c r="DA4" s="81"/>
+      <c r="DB4" s="81">
         <f>DB5</f>
         <v>46146</v>
       </c>
-      <c r="DC4" s="62"/>
-      <c r="DD4" s="62"/>
-      <c r="DE4" s="62"/>
-      <c r="DF4" s="62"/>
-      <c r="DG4" s="62"/>
-      <c r="DH4" s="62"/>
-      <c r="DI4" s="62">
+      <c r="DC4" s="81"/>
+      <c r="DD4" s="81"/>
+      <c r="DE4" s="81"/>
+      <c r="DF4" s="81"/>
+      <c r="DG4" s="81"/>
+      <c r="DH4" s="81"/>
+      <c r="DI4" s="81">
         <f>DI5</f>
         <v>46153</v>
       </c>
-      <c r="DJ4" s="62"/>
-      <c r="DK4" s="62"/>
-      <c r="DL4" s="62"/>
-      <c r="DM4" s="62"/>
-      <c r="DN4" s="62"/>
-      <c r="DO4" s="72"/>
+      <c r="DJ4" s="81"/>
+      <c r="DK4" s="81"/>
+      <c r="DL4" s="81"/>
+      <c r="DM4" s="81"/>
+      <c r="DN4" s="81"/>
+      <c r="DO4" s="84"/>
     </row>
-    <row r="5" spans="1:148" s="19" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="52"/>
-      <c r="B5" s="53" t="s">
+    <row r="5" spans="1:119" s="19" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="69"/>
+      <c r="B5" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="56" t="s">
+      <c r="C5" s="72" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="56" t="s">
+      <c r="D5" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="56" t="s">
+      <c r="E5" s="72" t="s">
         <v>3</v>
       </c>
       <c r="H5" s="21">
@@ -2378,7 +2067,7 @@
         <f t="shared" si="2"/>
         <v>46102</v>
       </c>
-      <c r="BK5" s="68">
+      <c r="BK5" s="53">
         <f t="shared" si="2"/>
         <v>46103</v>
       </c>
@@ -2602,17 +2291,17 @@
         <f t="shared" ref="DN5" si="41">DM5+1</f>
         <v>46158</v>
       </c>
-      <c r="DO5" s="68">
+      <c r="DO5" s="53">
         <f t="shared" ref="DO5" si="42">DN5+1</f>
         <v>46159</v>
       </c>
     </row>
-    <row r="6" spans="1:148" s="19" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="52"/>
-      <c r="B6" s="54"/>
-      <c r="C6" s="77"/>
-      <c r="D6" s="55"/>
-      <c r="E6" s="55"/>
+    <row r="6" spans="1:119" s="19" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="69"/>
+      <c r="B6" s="71"/>
+      <c r="C6" s="73"/>
+      <c r="D6" s="74"/>
+      <c r="E6" s="74"/>
       <c r="H6" s="24" t="str">
         <f t="shared" ref="H6:AM6" si="43">LEFT(TEXT(H5,"ddd"),1)</f>
         <v>M</v>
@@ -2833,7 +2522,7 @@
         <f t="shared" si="44"/>
         <v>S</v>
       </c>
-      <c r="BK6" s="69" t="str">
+      <c r="BK6" s="54" t="str">
         <f t="shared" si="44"/>
         <v>S</v>
       </c>
@@ -3057,17 +2746,17 @@
         <f t="shared" si="45"/>
         <v>S</v>
       </c>
-      <c r="DO6" s="69" t="str">
+      <c r="DO6" s="54" t="str">
         <f t="shared" si="45"/>
         <v>S</v>
       </c>
     </row>
-    <row r="7" spans="1:148" s="19" customFormat="1" ht="30" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:119" s="19" customFormat="1" ht="30" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="26"/>
-      <c r="C7" s="78"/>
+      <c r="C7" s="60"/>
       <c r="D7" s="26"/>
       <c r="E7" s="26"/>
       <c r="G7" s="19" t="str">
@@ -3130,14 +2819,14 @@
       <c r="BI7" s="27"/>
       <c r="BJ7" s="27"/>
       <c r="BK7" s="27"/>
-      <c r="DO7" s="71"/>
+      <c r="DO7" s="55"/>
     </row>
-    <row r="8" spans="1:148" s="29" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:119" s="29" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="13"/>
       <c r="B8" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="79">
+      <c r="C8" s="61">
         <f>E8-D8</f>
         <v>5</v>
       </c>
@@ -3264,43 +2953,14 @@
       <c r="DL8" s="32"/>
       <c r="DM8" s="32"/>
       <c r="DN8" s="32"/>
-      <c r="DO8" s="73"/>
-      <c r="DP8" s="70"/>
-      <c r="DQ8" s="70"/>
-      <c r="DR8" s="70"/>
-      <c r="DS8" s="70"/>
-      <c r="DT8" s="70"/>
-      <c r="DU8" s="70"/>
-      <c r="DV8" s="70"/>
-      <c r="DW8" s="70"/>
-      <c r="DX8" s="70"/>
-      <c r="DY8" s="70"/>
-      <c r="DZ8" s="70"/>
-      <c r="EA8" s="70"/>
-      <c r="EB8" s="70"/>
-      <c r="EC8" s="70"/>
-      <c r="ED8" s="70"/>
-      <c r="EE8" s="70"/>
-      <c r="EF8" s="70"/>
-      <c r="EG8" s="70"/>
-      <c r="EH8" s="70"/>
-      <c r="EI8" s="70"/>
-      <c r="EJ8" s="70"/>
-      <c r="EK8" s="70"/>
-      <c r="EL8" s="70"/>
-      <c r="EM8" s="70"/>
-      <c r="EN8" s="70"/>
-      <c r="EO8" s="70"/>
-      <c r="EP8" s="70"/>
-      <c r="EQ8" s="70"/>
-      <c r="ER8" s="70"/>
+      <c r="DO8" s="56"/>
     </row>
-    <row r="9" spans="1:148" s="29" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:119" s="29" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="13"/>
       <c r="B9" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="80">
+      <c r="C9" s="62">
         <f>E9-D9</f>
         <v>14</v>
       </c>
@@ -3426,43 +3086,14 @@
       <c r="DL9" s="32"/>
       <c r="DM9" s="32"/>
       <c r="DN9" s="32"/>
-      <c r="DO9" s="73"/>
-      <c r="DP9" s="70"/>
-      <c r="DQ9" s="70"/>
-      <c r="DR9" s="70"/>
-      <c r="DS9" s="70"/>
-      <c r="DT9" s="70"/>
-      <c r="DU9" s="70"/>
-      <c r="DV9" s="70"/>
-      <c r="DW9" s="70"/>
-      <c r="DX9" s="70"/>
-      <c r="DY9" s="70"/>
-      <c r="DZ9" s="70"/>
-      <c r="EA9" s="70"/>
-      <c r="EB9" s="70"/>
-      <c r="EC9" s="70"/>
-      <c r="ED9" s="70"/>
-      <c r="EE9" s="70"/>
-      <c r="EF9" s="70"/>
-      <c r="EG9" s="70"/>
-      <c r="EH9" s="70"/>
-      <c r="EI9" s="70"/>
-      <c r="EJ9" s="70"/>
-      <c r="EK9" s="70"/>
-      <c r="EL9" s="70"/>
-      <c r="EM9" s="70"/>
-      <c r="EN9" s="70"/>
-      <c r="EO9" s="70"/>
-      <c r="EP9" s="70"/>
-      <c r="EQ9" s="70"/>
-      <c r="ER9" s="70"/>
+      <c r="DO9" s="56"/>
     </row>
-    <row r="10" spans="1:148" s="29" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:119" s="29" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
       <c r="B10" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="81">
+      <c r="C10" s="63">
         <f>E10-D10</f>
         <v>28</v>
       </c>
@@ -3588,43 +3219,14 @@
       <c r="DL10" s="32"/>
       <c r="DM10" s="32"/>
       <c r="DN10" s="32"/>
-      <c r="DO10" s="73"/>
-      <c r="DP10" s="70"/>
-      <c r="DQ10" s="70"/>
-      <c r="DR10" s="70"/>
-      <c r="DS10" s="70"/>
-      <c r="DT10" s="70"/>
-      <c r="DU10" s="70"/>
-      <c r="DV10" s="70"/>
-      <c r="DW10" s="70"/>
-      <c r="DX10" s="70"/>
-      <c r="DY10" s="70"/>
-      <c r="DZ10" s="70"/>
-      <c r="EA10" s="70"/>
-      <c r="EB10" s="70"/>
-      <c r="EC10" s="70"/>
-      <c r="ED10" s="70"/>
-      <c r="EE10" s="70"/>
-      <c r="EF10" s="70"/>
-      <c r="EG10" s="70"/>
-      <c r="EH10" s="70"/>
-      <c r="EI10" s="70"/>
-      <c r="EJ10" s="70"/>
-      <c r="EK10" s="70"/>
-      <c r="EL10" s="70"/>
-      <c r="EM10" s="70"/>
-      <c r="EN10" s="70"/>
-      <c r="EO10" s="70"/>
-      <c r="EP10" s="70"/>
-      <c r="EQ10" s="70"/>
-      <c r="ER10" s="70"/>
+      <c r="DO10" s="56"/>
     </row>
-    <row r="11" spans="1:148" s="29" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:119" s="29" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="12"/>
       <c r="B11" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="82">
+      <c r="C11" s="64">
         <f>E11-D11</f>
         <v>25</v>
       </c>
@@ -3750,50 +3352,21 @@
       <c r="DL11" s="32"/>
       <c r="DM11" s="32"/>
       <c r="DN11" s="32"/>
-      <c r="DO11" s="73"/>
-      <c r="DP11" s="70"/>
-      <c r="DQ11" s="70"/>
-      <c r="DR11" s="70"/>
-      <c r="DS11" s="70"/>
-      <c r="DT11" s="70"/>
-      <c r="DU11" s="70"/>
-      <c r="DV11" s="70"/>
-      <c r="DW11" s="70"/>
-      <c r="DX11" s="70"/>
-      <c r="DY11" s="70"/>
-      <c r="DZ11" s="70"/>
-      <c r="EA11" s="70"/>
-      <c r="EB11" s="70"/>
-      <c r="EC11" s="70"/>
-      <c r="ED11" s="70"/>
-      <c r="EE11" s="70"/>
-      <c r="EF11" s="70"/>
-      <c r="EG11" s="70"/>
-      <c r="EH11" s="70"/>
-      <c r="EI11" s="70"/>
-      <c r="EJ11" s="70"/>
-      <c r="EK11" s="70"/>
-      <c r="EL11" s="70"/>
-      <c r="EM11" s="70"/>
-      <c r="EN11" s="70"/>
-      <c r="EO11" s="70"/>
-      <c r="EP11" s="70"/>
-      <c r="EQ11" s="70"/>
-      <c r="ER11" s="70"/>
+      <c r="DO11" s="56"/>
     </row>
-    <row r="12" spans="1:148" s="29" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:119" s="29" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>
-      <c r="B12" s="75" t="s">
+      <c r="B12" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="83">
+      <c r="C12" s="65">
         <f>E12-D12</f>
         <v>19</v>
       </c>
-      <c r="D12" s="76">
+      <c r="D12" s="59">
         <v>46127</v>
       </c>
-      <c r="E12" s="76">
+      <c r="E12" s="59">
         <v>46146</v>
       </c>
       <c r="F12" s="15"/>
@@ -3912,38 +3485,9 @@
       <c r="DL12" s="32"/>
       <c r="DM12" s="32"/>
       <c r="DN12" s="32"/>
-      <c r="DO12" s="73"/>
-      <c r="DP12" s="70"/>
-      <c r="DQ12" s="70"/>
-      <c r="DR12" s="70"/>
-      <c r="DS12" s="70"/>
-      <c r="DT12" s="70"/>
-      <c r="DU12" s="70"/>
-      <c r="DV12" s="70"/>
-      <c r="DW12" s="70"/>
-      <c r="DX12" s="70"/>
-      <c r="DY12" s="70"/>
-      <c r="DZ12" s="70"/>
-      <c r="EA12" s="70"/>
-      <c r="EB12" s="70"/>
-      <c r="EC12" s="70"/>
-      <c r="ED12" s="70"/>
-      <c r="EE12" s="70"/>
-      <c r="EF12" s="70"/>
-      <c r="EG12" s="70"/>
-      <c r="EH12" s="70"/>
-      <c r="EI12" s="70"/>
-      <c r="EJ12" s="70"/>
-      <c r="EK12" s="70"/>
-      <c r="EL12" s="70"/>
-      <c r="EM12" s="70"/>
-      <c r="EN12" s="70"/>
-      <c r="EO12" s="70"/>
-      <c r="EP12" s="70"/>
-      <c r="EQ12" s="70"/>
-      <c r="ER12" s="70"/>
+      <c r="DO12" s="56"/>
     </row>
-    <row r="13" spans="1:148" s="29" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:119" s="29" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13" s="39"/>
       <c r="C13" s="39"/>
@@ -4010,37 +3554,8 @@
       <c r="BI13" s="28"/>
       <c r="BJ13" s="28"/>
       <c r="BK13" s="28"/>
-      <c r="DP13" s="70"/>
-      <c r="DQ13" s="70"/>
-      <c r="DR13" s="70"/>
-      <c r="DS13" s="70"/>
-      <c r="DT13" s="70"/>
-      <c r="DU13" s="70"/>
-      <c r="DV13" s="70"/>
-      <c r="DW13" s="70"/>
-      <c r="DX13" s="70"/>
-      <c r="DY13" s="70"/>
-      <c r="DZ13" s="70"/>
-      <c r="EA13" s="70"/>
-      <c r="EB13" s="70"/>
-      <c r="EC13" s="70"/>
-      <c r="ED13" s="70"/>
-      <c r="EE13" s="70"/>
-      <c r="EF13" s="70"/>
-      <c r="EG13" s="70"/>
-      <c r="EH13" s="70"/>
-      <c r="EI13" s="70"/>
-      <c r="EJ13" s="70"/>
-      <c r="EK13" s="70"/>
-      <c r="EL13" s="70"/>
-      <c r="EM13" s="70"/>
-      <c r="EN13" s="70"/>
-      <c r="EO13" s="70"/>
-      <c r="EP13" s="70"/>
-      <c r="EQ13" s="70"/>
-      <c r="ER13" s="70"/>
     </row>
-    <row r="14" spans="1:148" s="29" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:119" s="29" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="41" t="s">
         <v>0</v>
@@ -4165,39 +3680,11 @@
       <c r="DM14" s="44"/>
       <c r="DN14" s="44"/>
       <c r="DO14" s="44"/>
-      <c r="DQ14" s="70"/>
-      <c r="DR14" s="70"/>
-      <c r="DS14" s="70"/>
-      <c r="DT14" s="70"/>
-      <c r="DU14" s="70"/>
-      <c r="DV14" s="70"/>
-      <c r="DW14" s="70"/>
-      <c r="DX14" s="70"/>
-      <c r="DY14" s="70"/>
-      <c r="DZ14" s="70"/>
-      <c r="EA14" s="70"/>
-      <c r="EB14" s="70"/>
-      <c r="EC14" s="70"/>
-      <c r="ED14" s="70"/>
-      <c r="EE14" s="70"/>
-      <c r="EF14" s="70"/>
-      <c r="EG14" s="70"/>
-      <c r="EH14" s="70"/>
-      <c r="EI14" s="70"/>
-      <c r="EJ14" s="70"/>
-      <c r="EK14" s="70"/>
-      <c r="EL14" s="70"/>
-      <c r="EM14" s="70"/>
-      <c r="EN14" s="70"/>
-      <c r="EO14" s="70"/>
-      <c r="EP14" s="70"/>
-      <c r="EQ14" s="70"/>
-      <c r="ER14" s="70"/>
     </row>
-    <row r="15" spans="1:148" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F15" s="3"/>
     </row>
-    <row r="16" spans="1:148" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:119" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E16" s="14"/>
     </row>
   </sheetData>
@@ -4218,7 +3705,6 @@
     <mergeCell ref="AJ4:AP4"/>
     <mergeCell ref="AQ4:AW4"/>
     <mergeCell ref="AX4:BD4"/>
-    <mergeCell ref="E5:E6"/>
     <mergeCell ref="P2:Y2"/>
     <mergeCell ref="P1:Y1"/>
     <mergeCell ref="H1:N1"/>
@@ -4228,42 +3714,43 @@
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
   </mergeCells>
-  <conditionalFormatting sqref="BL4:DO6 BL8:EO11 H4:BK11 H12:EO12">
-    <cfRule type="expression" dxfId="10" priority="3">
-      <formula>AND(TODAY()&gt;=H$5, TODAY()&lt;I$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="H8:EO8">
-    <cfRule type="expression" dxfId="9" priority="8">
+    <cfRule type="expression" dxfId="10" priority="8">
       <formula>AND(task_start&lt;=H$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=H$5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="9" priority="9" stopIfTrue="1">
       <formula>AND(task_end&gt;=H$5,task_start&lt;I$5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H9:EO9">
-    <cfRule type="expression" dxfId="7" priority="6">
+    <cfRule type="expression" dxfId="8" priority="6">
       <formula>AND(task_start&lt;=H$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=H$5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="7" priority="7" stopIfTrue="1">
       <formula>AND(task_end&gt;=H$5,task_start&lt;I$5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H10:EO10">
-    <cfRule type="expression" dxfId="5" priority="4">
+    <cfRule type="expression" dxfId="6" priority="4">
       <formula>AND(task_start&lt;=H$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=H$5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="5" stopIfTrue="1">
       <formula>AND(task_end&gt;=H$5,task_start&lt;I$5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11:EO11">
-    <cfRule type="expression" dxfId="3" priority="38">
+    <cfRule type="expression" dxfId="4" priority="38">
       <formula>AND(task_start&lt;=H$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=H$5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="39" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="39" stopIfTrue="1">
       <formula>AND(task_end&gt;=H$5,task_start&lt;I$5)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12:EO12 BL4:DO6 H4:BK11 BL8:EO11">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>AND(TODAY()&gt;=H$5, TODAY()&lt;I$5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12:EO12">
